--- a/research/traditional_assets/database/data/singapore/singapore_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0501</v>
+        <v>-0.0246</v>
       </c>
       <c r="E2">
-        <v>0.063</v>
+        <v>-0.0561</v>
       </c>
       <c r="G2">
-        <v>0.5466101694915254</v>
+        <v>0.6737160120845921</v>
       </c>
       <c r="H2">
-        <v>0.5466101694915254</v>
+        <v>0.6737160120845921</v>
       </c>
       <c r="I2">
-        <v>0.6165254237288136</v>
+        <v>0.4652567975830816</v>
       </c>
       <c r="J2">
-        <v>0.5044982430756512</v>
+        <v>0.3724682950142523</v>
       </c>
       <c r="K2">
-        <v>20.2</v>
+        <v>14.1</v>
       </c>
       <c r="L2">
-        <v>0.4279661016949152</v>
+        <v>0.4259818731117824</v>
       </c>
       <c r="M2">
-        <v>6.37</v>
+        <v>9.23</v>
       </c>
       <c r="N2">
-        <v>0.0205020920502092</v>
+        <v>0.03124576844955992</v>
       </c>
       <c r="O2">
-        <v>0.3153465346534653</v>
+        <v>0.6546099290780142</v>
       </c>
       <c r="P2">
-        <v>6.37</v>
+        <v>9.23</v>
       </c>
       <c r="Q2">
-        <v>0.0205020920502092</v>
+        <v>0.03124576844955992</v>
       </c>
       <c r="R2">
-        <v>0.3153465346534653</v>
+        <v>0.6546099290780142</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>33.5</v>
+        <v>19.6</v>
       </c>
       <c r="V2">
-        <v>0.1078210492436434</v>
+        <v>0.06635071090047394</v>
       </c>
       <c r="W2">
-        <v>0.06939196152524904</v>
+        <v>0.04271432899121478</v>
       </c>
       <c r="X2">
-        <v>0.04787508093102097</v>
+        <v>0.07977361111291688</v>
       </c>
       <c r="Y2">
-        <v>0.02151688059422807</v>
+        <v>-0.0370592821217021</v>
       </c>
       <c r="Z2">
-        <v>0.1858706781129401</v>
+        <v>0.1114459352536153</v>
       </c>
       <c r="AA2">
-        <v>0.09377143054725816</v>
+        <v>0.04151007749018283</v>
       </c>
       <c r="AB2">
-        <v>0.04783798216374194</v>
+        <v>0.07977059400029668</v>
       </c>
       <c r="AC2">
-        <v>0.04593344838351621</v>
+        <v>-0.03826051651011385</v>
       </c>
       <c r="AD2">
-        <v>0.405</v>
+        <v>0.022</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.405</v>
+        <v>0.022</v>
       </c>
       <c r="AG2">
-        <v>-33.095</v>
+        <v>-19.578</v>
       </c>
       <c r="AH2">
-        <v>0.001301811285578824</v>
+        <v>7.446974158999668e-05</v>
       </c>
       <c r="AI2">
-        <v>0.001225397497768566</v>
+        <v>7.296316686676262e-05</v>
       </c>
       <c r="AJ2">
-        <v>-0.1192161524468219</v>
+        <v>-0.0709805599263293</v>
       </c>
       <c r="AK2">
-        <v>-0.1114291005201933</v>
+        <v>-0.06944474003447762</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.01372881355932203</v>
+        <v>0.00141025641025641</v>
       </c>
       <c r="AP2">
-        <v>-1.121864406779661</v>
+        <v>-1.255</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +716,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0501</v>
+        <v>-0.0246</v>
       </c>
       <c r="E3">
-        <v>0.063</v>
+        <v>-0.0561</v>
       </c>
       <c r="G3">
-        <v>0.5466101694915254</v>
+        <v>0.6737160120845921</v>
       </c>
       <c r="H3">
-        <v>0.5466101694915254</v>
+        <v>0.6737160120845921</v>
       </c>
       <c r="I3">
-        <v>0.6165254237288136</v>
+        <v>0.4652567975830816</v>
       </c>
       <c r="J3">
-        <v>0.5044982430756512</v>
+        <v>0.3724682950142523</v>
       </c>
       <c r="K3">
-        <v>20.2</v>
+        <v>14.1</v>
       </c>
       <c r="L3">
-        <v>0.4279661016949152</v>
+        <v>0.4259818731117824</v>
       </c>
       <c r="M3">
-        <v>6.37</v>
+        <v>9.23</v>
       </c>
       <c r="N3">
-        <v>0.0205020920502092</v>
+        <v>0.03124576844955992</v>
       </c>
       <c r="O3">
-        <v>0.3153465346534653</v>
+        <v>0.6546099290780142</v>
       </c>
       <c r="P3">
-        <v>6.37</v>
+        <v>9.23</v>
       </c>
       <c r="Q3">
-        <v>0.0205020920502092</v>
+        <v>0.03124576844955992</v>
       </c>
       <c r="R3">
-        <v>0.3153465346534653</v>
+        <v>0.6546099290780142</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>33.5</v>
+        <v>19.6</v>
       </c>
       <c r="V3">
-        <v>0.1078210492436434</v>
+        <v>0.06635071090047394</v>
       </c>
       <c r="W3">
-        <v>0.06939196152524904</v>
+        <v>0.04271432899121478</v>
       </c>
       <c r="X3">
-        <v>0.04787508093102097</v>
+        <v>0.07977361111291688</v>
       </c>
       <c r="Y3">
-        <v>0.02151688059422807</v>
+        <v>-0.0370592821217021</v>
       </c>
       <c r="Z3">
-        <v>0.1858706781129401</v>
+        <v>0.1114459352536153</v>
       </c>
       <c r="AA3">
-        <v>0.09377143054725816</v>
+        <v>0.04151007749018283</v>
       </c>
       <c r="AB3">
-        <v>0.04783798216374194</v>
+        <v>0.07977059400029668</v>
       </c>
       <c r="AC3">
-        <v>0.04593344838351621</v>
+        <v>-0.03826051651011385</v>
       </c>
       <c r="AD3">
-        <v>0.405</v>
+        <v>0.022</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.405</v>
+        <v>0.022</v>
       </c>
       <c r="AG3">
-        <v>-33.095</v>
+        <v>-19.578</v>
       </c>
       <c r="AH3">
-        <v>0.001301811285578824</v>
+        <v>7.446974158999668e-05</v>
       </c>
       <c r="AI3">
-        <v>0.001225397497768566</v>
+        <v>7.296316686676262e-05</v>
       </c>
       <c r="AJ3">
-        <v>-0.1192161524468219</v>
+        <v>-0.0709805599263293</v>
       </c>
       <c r="AK3">
-        <v>-0.1114291005201933</v>
+        <v>-0.06944474003447762</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.01372881355932203</v>
+        <v>0.00141025641025641</v>
       </c>
       <c r="AP3">
-        <v>-1.121864406779661</v>
+        <v>-1.255</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/singapore/singapore_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0246</v>
+        <v>0.0132</v>
       </c>
       <c r="E2">
-        <v>-0.0561</v>
+        <v>-0.0571</v>
       </c>
       <c r="G2">
-        <v>0.6737160120845921</v>
+        <v>0.2494226327944573</v>
       </c>
       <c r="H2">
-        <v>0.6737160120845921</v>
+        <v>0.2494226327944573</v>
       </c>
       <c r="I2">
-        <v>0.4652567975830816</v>
+        <v>0.3903002309468822</v>
       </c>
       <c r="J2">
-        <v>0.3724682950142523</v>
+        <v>0.3022469904385759</v>
       </c>
       <c r="K2">
-        <v>14.1</v>
+        <v>16.1</v>
       </c>
       <c r="L2">
-        <v>0.4259818731117824</v>
+        <v>0.371824480369515</v>
       </c>
       <c r="M2">
-        <v>9.23</v>
+        <v>5.87</v>
       </c>
       <c r="N2">
-        <v>0.03124576844955992</v>
+        <v>0.02132994186046512</v>
       </c>
       <c r="O2">
-        <v>0.6546099290780142</v>
+        <v>0.3645962732919255</v>
       </c>
       <c r="P2">
-        <v>9.23</v>
+        <v>5.87</v>
       </c>
       <c r="Q2">
-        <v>0.03124576844955992</v>
+        <v>0.02132994186046512</v>
       </c>
       <c r="R2">
-        <v>0.6546099290780142</v>
+        <v>0.3645962732919255</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,67 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>19.6</v>
+        <v>37</v>
       </c>
       <c r="V2">
-        <v>0.06635071090047394</v>
+        <v>0.1344476744186047</v>
       </c>
       <c r="W2">
-        <v>0.04271432899121478</v>
+        <v>0.05339966832504146</v>
       </c>
       <c r="X2">
-        <v>0.07977361111291688</v>
+        <v>0.06917701170159493</v>
       </c>
       <c r="Y2">
-        <v>-0.0370592821217021</v>
+        <v>-0.01577734337655347</v>
       </c>
       <c r="Z2">
-        <v>0.1114459352536153</v>
+        <v>0.1535885812387824</v>
       </c>
       <c r="AA2">
-        <v>0.04151007749018283</v>
+        <v>0.0464216864451527</v>
       </c>
       <c r="AB2">
-        <v>0.07977059400029668</v>
+        <v>0.06917481695809129</v>
       </c>
       <c r="AC2">
-        <v>-0.03826051651011385</v>
+        <v>-0.02275313051293859</v>
       </c>
       <c r="AD2">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="AG2">
-        <v>-19.578</v>
+        <v>-36.981</v>
       </c>
       <c r="AH2">
-        <v>7.446974158999668e-05</v>
+        <v>6.903593138555114e-05</v>
       </c>
       <c r="AI2">
-        <v>7.296316686676262e-05</v>
+        <v>6.027555445579105e-05</v>
       </c>
       <c r="AJ2">
-        <v>-0.0709805599263293</v>
+        <v>-0.155239506504519</v>
       </c>
       <c r="AK2">
-        <v>-0.06944474003447762</v>
+        <v>-0.1329204691268389</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="AN2">
-        <v>0.00141025641025641</v>
+        <v>0.001061452513966481</v>
+      </c>
+      <c r="AO2">
+        <v>203.6144578313253</v>
       </c>
       <c r="AP2">
-        <v>-1.255</v>
+        <v>-2.065977653631285</v>
+      </c>
+      <c r="AQ2">
+        <v>203.6144578313253</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0246</v>
+        <v>0.0132</v>
       </c>
       <c r="E3">
-        <v>-0.0561</v>
+        <v>-0.0571</v>
       </c>
       <c r="G3">
-        <v>0.6737160120845921</v>
+        <v>0.2494226327944573</v>
       </c>
       <c r="H3">
-        <v>0.6737160120845921</v>
+        <v>0.2494226327944573</v>
       </c>
       <c r="I3">
-        <v>0.4652567975830816</v>
+        <v>0.3903002309468822</v>
       </c>
       <c r="J3">
-        <v>0.3724682950142523</v>
+        <v>0.3022469904385759</v>
       </c>
       <c r="K3">
-        <v>14.1</v>
+        <v>16.1</v>
       </c>
       <c r="L3">
-        <v>0.4259818731117824</v>
+        <v>0.371824480369515</v>
       </c>
       <c r="M3">
-        <v>9.23</v>
+        <v>5.87</v>
       </c>
       <c r="N3">
-        <v>0.03124576844955992</v>
+        <v>0.02132994186046512</v>
       </c>
       <c r="O3">
-        <v>0.6546099290780142</v>
+        <v>0.3645962732919255</v>
       </c>
       <c r="P3">
-        <v>9.23</v>
+        <v>5.87</v>
       </c>
       <c r="Q3">
-        <v>0.03124576844955992</v>
+        <v>0.02132994186046512</v>
       </c>
       <c r="R3">
-        <v>0.6546099290780142</v>
+        <v>0.3645962732919255</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,67 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>19.6</v>
+        <v>37</v>
       </c>
       <c r="V3">
-        <v>0.06635071090047394</v>
+        <v>0.1344476744186047</v>
       </c>
       <c r="W3">
-        <v>0.04271432899121478</v>
+        <v>0.05339966832504146</v>
       </c>
       <c r="X3">
-        <v>0.07977361111291688</v>
+        <v>0.06917701170159493</v>
       </c>
       <c r="Y3">
-        <v>-0.0370592821217021</v>
+        <v>-0.01577734337655347</v>
       </c>
       <c r="Z3">
-        <v>0.1114459352536153</v>
+        <v>0.1535885812387824</v>
       </c>
       <c r="AA3">
-        <v>0.04151007749018283</v>
+        <v>0.0464216864451527</v>
       </c>
       <c r="AB3">
-        <v>0.07977059400029668</v>
+        <v>0.06917481695809129</v>
       </c>
       <c r="AC3">
-        <v>-0.03826051651011385</v>
+        <v>-0.02275313051293859</v>
       </c>
       <c r="AD3">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="AG3">
-        <v>-19.578</v>
+        <v>-36.981</v>
       </c>
       <c r="AH3">
-        <v>7.446974158999668e-05</v>
+        <v>6.903593138555114e-05</v>
       </c>
       <c r="AI3">
-        <v>7.296316686676262e-05</v>
+        <v>6.027555445579105e-05</v>
       </c>
       <c r="AJ3">
-        <v>-0.0709805599263293</v>
+        <v>-0.155239506504519</v>
       </c>
       <c r="AK3">
-        <v>-0.06944474003447762</v>
+        <v>-0.1329204691268389</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="AN3">
-        <v>0.00141025641025641</v>
+        <v>0.001061452513966481</v>
+      </c>
+      <c r="AO3">
+        <v>203.6144578313253</v>
       </c>
       <c r="AP3">
-        <v>-1.255</v>
+        <v>-2.065977653631285</v>
+      </c>
+      <c r="AQ3">
+        <v>203.6144578313253</v>
       </c>
     </row>
   </sheetData>
